--- a/assets/template_materi.xlsx
+++ b/assets/template_materi.xlsx
@@ -1,56 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Petunjuk" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Petunjuk" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
+  <definedNames/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDDDDD"/>
+        <bgColor rgb="00DDDDDD"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -65,14 +51,82 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -397,146 +451,231 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="75.83203125" customWidth="1"/>
-    <col min="2" max="2" width="24.83203125" customWidth="1"/>
+    <col width="75.83203125" customWidth="1" min="1" max="1"/>
+    <col width="24.83203125" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>Caption</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Media_Name</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Nama_Akun</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Caption</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Media_Name</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>{Halo|Hai|Assalamualaikum} bunda 👋 {ready|stok ready} hari ini!</v>
-      </c>
-      <c r="B2" t="str">
-        <v>foto1.jpg</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Akun_A</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>{Halo|Hai|Assalamualaikum} bunda 👋 {ready|stok ready} hari ini!</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>foto1.jpg</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>Promo {gamis|daster} murah, cek katalog {sekarang|hari ini} ya!</v>
-      </c>
-      <c r="B3" t="str">
-        <v>foto2.jpg</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Akun_B</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Promo {gamis|daster} murah, cek katalog {sekarang|hari ini} ya!</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>foto2.jpg</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>Materi {edukasi|tips} gratis. Simpan &amp; cek link di {bio|deskripsi} kami.</v>
-      </c>
-      <c r="B4" t="str">
-        <v>edukasi.png</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Akun_A</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Materi {edukasi|tips} gratis. Simpan &amp; cek link di {bio|deskripsi} kami.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>edukasi.png</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
-        <v>Postingan teks tanpa media, hanya caption.</v>
-      </c>
-      <c r="B5" t="str">
-        <v/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Akun_A</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Postingan teks tanpa media, hanya caption.</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="str">
-        <v>{Langsung|Seketika} {dikirim|diproses} orderan anda. #promo #gratisongkir</v>
-      </c>
-      <c r="B6" t="str">
-        <v>video1.mp4</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Akun_B</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>{Langsung|Seketika} {dikirim|diproses} orderan anda. #promo #gratisongkir</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>video1.mp4</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B6"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.83203125" customWidth="1"/>
-    <col min="2" max="2" width="90.83203125" customWidth="1"/>
+    <col width="4.83203125" customWidth="1" min="1" max="1"/>
+    <col width="90.83203125" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>PETUNJUK FORMAT EXCEL — FB AUTO POSTER</v>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>PETUNJUK FORMAT EXCEL — FB AUTO POSTER</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>1</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Nama kolom WAJIB: Caption (harus ada).</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Nama kolom WAJIB: Caption (harus ada).</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>2</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Nama kolom media: Media_Name ATAU Media (opsional).</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Nama kolom media: Media_Name ATAU Media (opsional).</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
-        <v>3</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Header/baris judul WAJIB di baris pertama.</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Header/baris judul WAJIB di baris pertama.</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="str">
-        <v>4</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Data harus di SHEET PERTAMA (Sheet1).</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Data harus di SHEET PERTAMA (Sheet1).</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="str">
-        <v>SPINTAX ({pilihan1|pilihan2|...}) akan diacak otomatis tiap posting.</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SPINTAX ({pilihan1|pilihan2|...}) akan diacak otomatis tiap posting.</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="str">
-        <v>Contoh: {Halo|Hai} {bunda|sis} -&gt; hasil acak mis. 'Hai sis'.</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Contoh: {Halo|Hai} {bunda|sis} -&gt; hasil acak mis. 'Hai sis'.</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="str">
-        <v>Media_Name berisi NAMA FILE saja (bukan path).</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Media_Name berisi NAMA FILE saja (bukan path).</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="str">
-        <v>Contoh: foto1.jpg (harus cocok dengan file di folder media).</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Contoh: foto1.jpg (harus cocok dengan file di folder media).</t>
+        </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="str">
-        <v>Kosongkan Media_Name untuk posting teks tanpa media.</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Kosongkan Media_Name untuk posting teks tanpa media.</t>
+        </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="str">
-        <v>Kolom lain (No, Kategori, Note, dll.) akan DIIGNOR di alat.</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Kolom lain (No, Kategori, Note, dll.) akan DIIGNOR di alat.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B15"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>